--- a/Data/EXCEL/Transfer/salemon/202208/6794-salemon-202208.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202208/6794-salemon-202208.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WORKSPACES\GoodinfoWebData\salemon\202208\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WORKSPACES\xls2xlsx\Transfer\202208\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{67888B27-A0A0-4CB1-A74A-634C59D4FEC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6875A266-64AE-4FE1-A220-8A7C17FE41BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="1395" windowWidth="22035" windowHeight="12855"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="30645" windowHeight="19905"/>
   </bookViews>
   <sheets>
     <sheet name="6794-salemon-202208" sheetId="2" r:id="rId1"/>
@@ -80,7 +80,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="25">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -246,7 +246,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -261,9 +261,9 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF008000"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -271,13 +271,21 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF008000"/>
+      <color rgb="FFFF0000"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="新細明體"/>
       <family val="2"/>
       <charset val="136"/>
@@ -818,7 +826,7 @@
     <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -827,7 +835,7 @@
     <xf numFmtId="0" fontId="20" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="17" fontId="19" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -845,22 +853,22 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1218,24 +1226,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q28"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <dimension ref="A1:Q29"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.125" customWidth="1"/>
-    <col min="2" max="5" width="9.5" customWidth="1"/>
-    <col min="6" max="6" width="8" customWidth="1"/>
-    <col min="7" max="7" width="10.375" customWidth="1"/>
-    <col min="8" max="8" width="11" customWidth="1"/>
-    <col min="9" max="10" width="9.5" customWidth="1"/>
-    <col min="11" max="11" width="11" customWidth="1"/>
-    <col min="12" max="12" width="9.5" customWidth="1"/>
-    <col min="13" max="13" width="11" customWidth="1"/>
-    <col min="14" max="15" width="9.5" customWidth="1"/>
-    <col min="16" max="16" width="11" customWidth="1"/>
-    <col min="17" max="17" width="10.25" customWidth="1"/>
+    <col min="1" max="1" width="15.875" customWidth="1"/>
+    <col min="2" max="5" width="13.25" customWidth="1"/>
+    <col min="6" max="6" width="12.625" customWidth="1"/>
+    <col min="7" max="7" width="14.5" customWidth="1"/>
+    <col min="8" max="8" width="15.125" customWidth="1"/>
+    <col min="9" max="10" width="13.25" customWidth="1"/>
+    <col min="11" max="11" width="15.125" customWidth="1"/>
+    <col min="12" max="12" width="13.25" customWidth="1"/>
+    <col min="13" max="13" width="15.125" customWidth="1"/>
+    <col min="14" max="15" width="13.25" customWidth="1"/>
+    <col min="16" max="16" width="15.125" customWidth="1"/>
+    <col min="17" max="17" width="14.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="1" customFormat="1" ht="16.5" customHeight="1">
+    <row r="1" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -1262,7 +1270,7 @@
       <c r="P1" s="15"/>
       <c r="Q1" s="16"/>
     </row>
-    <row r="2" spans="1:17" s="1" customFormat="1" ht="16.5" customHeight="1">
+    <row r="2" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="12"/>
       <c r="B2" s="11" t="s">
         <v>4</v>
@@ -1301,7 +1309,7 @@
       </c>
       <c r="Q2" s="16"/>
     </row>
-    <row r="3" spans="1:17" s="1" customFormat="1">
+    <row r="3" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="12"/>
       <c r="B3" s="12"/>
       <c r="C3" s="12"/>
@@ -1344,7 +1352,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:17" s="1" customFormat="1">
+    <row r="4" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="13"/>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -1383,1122 +1391,1122 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:17" s="5" customFormat="1">
+    <row r="5" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
-        <v>44743</v>
+        <v>44774</v>
       </c>
       <c r="B5" s="7">
-        <v>34.9</v>
+        <v>35.9</v>
       </c>
       <c r="C5" s="7">
-        <v>35.9</v>
+        <v>34.950000000000003</v>
       </c>
       <c r="D5" s="7">
         <v>36</v>
       </c>
       <c r="E5" s="7">
+        <v>33.25</v>
+      </c>
+      <c r="F5" s="8">
+        <v>-0.95</v>
+      </c>
+      <c r="G5" s="8">
+        <v>-2.65</v>
+      </c>
+      <c r="H5" s="9">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="I5" s="8">
+        <v>-14.1</v>
+      </c>
+      <c r="J5" s="10">
+        <v>53.6</v>
+      </c>
+      <c r="K5" s="9">
+        <v>9.7199999999999995E-2</v>
+      </c>
+      <c r="L5" s="10">
+        <v>84.1</v>
+      </c>
+      <c r="M5" s="9">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="N5" s="8">
+        <v>-14.1</v>
+      </c>
+      <c r="O5" s="10">
+        <v>53.6</v>
+      </c>
+      <c r="P5" s="9">
+        <v>9.7199999999999995E-2</v>
+      </c>
+      <c r="Q5" s="10">
+        <v>84.1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A6" s="6">
+        <v>44743</v>
+      </c>
+      <c r="B6" s="7">
+        <v>34.9</v>
+      </c>
+      <c r="C6" s="7">
+        <v>35.9</v>
+      </c>
+      <c r="D6" s="7">
+        <v>36</v>
+      </c>
+      <c r="E6" s="7">
         <v>32</v>
       </c>
-      <c r="F5" s="8">
+      <c r="F6" s="10">
         <v>1</v>
       </c>
-      <c r="G5" s="8">
+      <c r="G6" s="10">
         <v>2.87</v>
       </c>
-      <c r="H5" s="9">
+      <c r="H6" s="9">
         <v>8.0999999999999996E-3</v>
       </c>
-      <c r="I5" s="8">
+      <c r="I6" s="10">
         <v>303</v>
       </c>
-      <c r="J5" s="10">
+      <c r="J6" s="8">
         <v>-13.9</v>
       </c>
-      <c r="K5" s="9">
+      <c r="K6" s="9">
         <v>9.0200000000000002E-2</v>
       </c>
-      <c r="L5" s="8">
+      <c r="L6" s="10">
         <v>87</v>
       </c>
-      <c r="M5" s="9">
+      <c r="M6" s="9">
         <v>8.0999999999999996E-3</v>
       </c>
-      <c r="N5" s="8">
+      <c r="N6" s="10">
         <v>303</v>
       </c>
-      <c r="O5" s="10">
+      <c r="O6" s="8">
         <v>-13.9</v>
       </c>
-      <c r="P5" s="9">
+      <c r="P6" s="9">
         <v>9.0200000000000002E-2</v>
       </c>
-      <c r="Q5" s="8">
+      <c r="Q6" s="10">
         <v>87</v>
       </c>
     </row>
-    <row r="6" spans="1:17" s="5" customFormat="1">
-      <c r="A6" s="6">
+    <row r="7" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A7" s="6">
         <v>44713</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B7" s="7">
         <v>33.5</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C7" s="7">
         <v>34.9</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D7" s="7">
         <v>35.25</v>
       </c>
-      <c r="E6" s="7">
+      <c r="E7" s="7">
         <v>31.3</v>
       </c>
-      <c r="F6" s="8">
+      <c r="F7" s="10">
         <v>1.4</v>
       </c>
-      <c r="G6" s="8">
+      <c r="G7" s="10">
         <v>4.18</v>
       </c>
-      <c r="H6" s="9">
+      <c r="H7" s="9">
         <v>2E-3</v>
       </c>
-      <c r="I6" s="10">
+      <c r="I7" s="8">
         <v>-89.7</v>
       </c>
-      <c r="J6" s="10">
+      <c r="J7" s="8">
         <v>-56.7</v>
       </c>
-      <c r="K6" s="9">
+      <c r="K7" s="9">
         <v>8.2100000000000006E-2</v>
       </c>
-      <c r="L6" s="8">
+      <c r="L7" s="10">
         <v>111.5</v>
       </c>
-      <c r="M6" s="9">
+      <c r="M7" s="9">
         <v>2E-3</v>
       </c>
-      <c r="N6" s="10">
+      <c r="N7" s="8">
         <v>-89.7</v>
       </c>
-      <c r="O6" s="10">
+      <c r="O7" s="8">
         <v>-56.7</v>
       </c>
-      <c r="P6" s="9">
+      <c r="P7" s="9">
         <v>8.2100000000000006E-2</v>
       </c>
-      <c r="Q6" s="8">
+      <c r="Q7" s="10">
         <v>111.5</v>
       </c>
     </row>
-    <row r="7" spans="1:17" s="5" customFormat="1">
-      <c r="A7" s="6">
+    <row r="8" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A8" s="6">
         <v>44682</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B8" s="7">
         <v>34.799999999999997</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C8" s="7">
         <v>33.5</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D8" s="7">
         <v>34.9</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E8" s="7">
         <v>31.6</v>
       </c>
-      <c r="F7" s="10">
+      <c r="F8" s="8">
         <v>-1.3</v>
       </c>
-      <c r="G7" s="10">
+      <c r="G8" s="8">
         <v>-3.74</v>
       </c>
-      <c r="H7" s="9">
+      <c r="H8" s="9">
         <v>1.9599999999999999E-2</v>
       </c>
-      <c r="I7" s="8">
+      <c r="I8" s="10">
         <v>55.8</v>
       </c>
-      <c r="J7" s="8">
+      <c r="J8" s="10">
         <v>194.4</v>
       </c>
-      <c r="K7" s="9">
+      <c r="K8" s="9">
         <v>8.0100000000000005E-2</v>
       </c>
-      <c r="L7" s="8">
+      <c r="L8" s="10">
         <v>134.30000000000001</v>
       </c>
-      <c r="M7" s="9">
+      <c r="M8" s="9">
         <v>1.9599999999999999E-2</v>
       </c>
-      <c r="N7" s="8">
+      <c r="N8" s="10">
         <v>55.8</v>
       </c>
-      <c r="O7" s="8">
+      <c r="O8" s="10">
         <v>194.4</v>
       </c>
-      <c r="P7" s="9">
+      <c r="P8" s="9">
         <v>8.0100000000000005E-2</v>
       </c>
-      <c r="Q7" s="8">
+      <c r="Q8" s="10">
         <v>134.30000000000001</v>
       </c>
     </row>
-    <row r="8" spans="1:17" s="5" customFormat="1">
-      <c r="A8" s="6">
+    <row r="9" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A9" s="6">
         <v>44652</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B9" s="7">
         <v>35.200000000000003</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C9" s="7">
         <v>34.799999999999997</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D9" s="7">
         <v>36.6</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E9" s="7">
         <v>33.25</v>
       </c>
-      <c r="F8" s="10">
+      <c r="F9" s="8">
         <v>-0.4</v>
       </c>
-      <c r="G8" s="10">
+      <c r="G9" s="8">
         <v>-1.1399999999999999</v>
       </c>
-      <c r="H8" s="9">
+      <c r="H9" s="9">
         <v>1.26E-2</v>
       </c>
-      <c r="I8" s="10">
+      <c r="I9" s="8">
         <v>-53.6</v>
       </c>
-      <c r="J8" s="8">
+      <c r="J9" s="10">
         <v>61.2</v>
       </c>
-      <c r="K8" s="9">
+      <c r="K9" s="9">
         <v>6.0499999999999998E-2</v>
       </c>
-      <c r="L8" s="8">
+      <c r="L9" s="10">
         <v>119.8</v>
       </c>
-      <c r="M8" s="9">
+      <c r="M9" s="9">
         <v>1.26E-2</v>
       </c>
-      <c r="N8" s="10">
+      <c r="N9" s="8">
         <v>-53.6</v>
       </c>
-      <c r="O8" s="8">
+      <c r="O9" s="10">
         <v>61.2</v>
       </c>
-      <c r="P8" s="9">
+      <c r="P9" s="9">
         <v>6.0499999999999998E-2</v>
       </c>
-      <c r="Q8" s="8">
+      <c r="Q9" s="10">
         <v>119.8</v>
       </c>
     </row>
-    <row r="9" spans="1:17" s="5" customFormat="1">
-      <c r="A9" s="6">
+    <row r="10" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A10" s="6">
         <v>44621</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B10" s="7">
         <v>36</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C10" s="7">
         <v>35.200000000000003</v>
       </c>
-      <c r="D9" s="7">
+      <c r="D10" s="7">
         <v>36.299999999999997</v>
       </c>
-      <c r="E9" s="7">
+      <c r="E10" s="7">
         <v>34.299999999999997</v>
       </c>
-      <c r="F9" s="10">
+      <c r="F10" s="8">
         <v>-0.8</v>
       </c>
-      <c r="G9" s="10">
+      <c r="G10" s="8">
         <v>-2.2200000000000002</v>
       </c>
-      <c r="H9" s="9">
+      <c r="H10" s="9">
         <v>2.7099999999999999E-2</v>
       </c>
-      <c r="I9" s="8">
+      <c r="I10" s="10">
         <v>84</v>
       </c>
-      <c r="J9" s="8">
+      <c r="J10" s="10">
         <v>306.60000000000002</v>
       </c>
-      <c r="K9" s="9">
+      <c r="K10" s="9">
         <v>4.7899999999999998E-2</v>
       </c>
-      <c r="L9" s="8">
+      <c r="L10" s="10">
         <v>142.9</v>
       </c>
-      <c r="M9" s="9">
+      <c r="M10" s="9">
         <v>2.7099999999999999E-2</v>
       </c>
-      <c r="N9" s="8">
+      <c r="N10" s="10">
         <v>84</v>
       </c>
-      <c r="O9" s="8">
+      <c r="O10" s="10">
         <v>306.60000000000002</v>
       </c>
-      <c r="P9" s="9">
+      <c r="P10" s="9">
         <v>4.7899999999999998E-2</v>
       </c>
-      <c r="Q9" s="8">
+      <c r="Q10" s="10">
         <v>142.9</v>
       </c>
     </row>
-    <row r="10" spans="1:17" s="5" customFormat="1">
-      <c r="A10" s="6">
+    <row r="11" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A11" s="6">
         <v>44593</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B11" s="7">
         <v>36.299999999999997</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C11" s="7">
         <v>36</v>
       </c>
-      <c r="D10" s="7">
+      <c r="D11" s="7">
         <v>38.299999999999997</v>
       </c>
-      <c r="E10" s="7">
+      <c r="E11" s="7">
         <v>35</v>
       </c>
-      <c r="F10" s="10">
+      <c r="F11" s="8">
         <v>-0.3</v>
       </c>
-      <c r="G10" s="10">
+      <c r="G11" s="8">
         <v>-0.83</v>
       </c>
-      <c r="H10" s="9">
+      <c r="H11" s="9">
         <v>1.47E-2</v>
       </c>
-      <c r="I10" s="8">
+      <c r="I11" s="10">
         <v>140.1</v>
       </c>
-      <c r="J10" s="8">
+      <c r="J11" s="10">
         <v>385.8</v>
       </c>
-      <c r="K10" s="9">
+      <c r="K11" s="9">
         <v>2.0799999999999999E-2</v>
       </c>
-      <c r="L10" s="8">
+      <c r="L11" s="10">
         <v>59.5</v>
       </c>
-      <c r="M10" s="9">
+      <c r="M11" s="9">
         <v>1.47E-2</v>
       </c>
-      <c r="N10" s="8">
+      <c r="N11" s="10">
         <v>140.1</v>
       </c>
-      <c r="O10" s="8">
+      <c r="O11" s="10">
         <v>385.8</v>
       </c>
-      <c r="P10" s="9">
+      <c r="P11" s="9">
         <v>2.0799999999999999E-2</v>
       </c>
-      <c r="Q10" s="8">
+      <c r="Q11" s="10">
         <v>59.5</v>
       </c>
     </row>
-    <row r="11" spans="1:17" s="5" customFormat="1">
-      <c r="A11" s="6">
+    <row r="12" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A12" s="6">
         <v>44562</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B12" s="7">
         <v>43.3</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C12" s="7">
         <v>36.299999999999997</v>
       </c>
-      <c r="D11" s="7">
+      <c r="D12" s="7">
         <v>43.3</v>
       </c>
-      <c r="E11" s="7">
+      <c r="E12" s="7">
         <v>34.700000000000003</v>
       </c>
-      <c r="F11" s="10">
+      <c r="F12" s="8">
         <v>-7</v>
       </c>
-      <c r="G11" s="10">
+      <c r="G12" s="8">
         <v>-16.170000000000002</v>
       </c>
-      <c r="H11" s="9">
+      <c r="H12" s="9">
         <v>6.1000000000000004E-3</v>
       </c>
-      <c r="I11" s="8">
+      <c r="I12" s="10">
         <v>117.4</v>
       </c>
-      <c r="J11" s="10">
+      <c r="J12" s="8">
         <v>-38.9</v>
       </c>
-      <c r="K11" s="9">
+      <c r="K12" s="9">
         <v>6.1000000000000004E-3</v>
       </c>
-      <c r="L11" s="10">
+      <c r="L12" s="8">
         <v>-38.9</v>
       </c>
-      <c r="M11" s="9">
+      <c r="M12" s="9">
         <v>6.1000000000000004E-3</v>
       </c>
-      <c r="N11" s="8">
+      <c r="N12" s="10">
         <v>117.4</v>
       </c>
-      <c r="O11" s="10">
+      <c r="O12" s="8">
         <v>-38.9</v>
       </c>
-      <c r="P11" s="9">
+      <c r="P12" s="9">
         <v>6.1000000000000004E-3</v>
       </c>
-      <c r="Q11" s="10">
+      <c r="Q12" s="8">
         <v>-38.9</v>
       </c>
     </row>
-    <row r="12" spans="1:17" s="5" customFormat="1">
-      <c r="A12" s="6">
+    <row r="13" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A13" s="6">
         <v>44531</v>
       </c>
-      <c r="B12" s="7">
+      <c r="B13" s="7">
         <v>40.5</v>
       </c>
-      <c r="C12" s="7">
+      <c r="C13" s="7">
         <v>43.3</v>
       </c>
-      <c r="D12" s="7">
+      <c r="D13" s="7">
         <v>46.4</v>
       </c>
-      <c r="E12" s="7">
+      <c r="E13" s="7">
         <v>40.799999999999997</v>
       </c>
-      <c r="F12" s="8">
+      <c r="F13" s="10">
         <v>2.8</v>
       </c>
-      <c r="G12" s="8">
+      <c r="G13" s="10">
         <v>6.91</v>
       </c>
-      <c r="H12" s="9">
+      <c r="H13" s="9">
         <v>2.8E-3</v>
       </c>
-      <c r="I12" s="10">
+      <c r="I13" s="8">
         <v>-48.7</v>
       </c>
-      <c r="J12" s="10">
+      <c r="J13" s="8">
         <v>-40.9</v>
       </c>
-      <c r="K12" s="9">
+      <c r="K13" s="9">
         <v>8.1799999999999998E-2</v>
       </c>
-      <c r="L12" s="8">
+      <c r="L13" s="10">
         <v>105.3</v>
       </c>
-      <c r="M12" s="9">
+      <c r="M13" s="9">
         <v>2.8E-3</v>
       </c>
-      <c r="N12" s="10">
+      <c r="N13" s="8">
         <v>-48.7</v>
       </c>
-      <c r="O12" s="10">
+      <c r="O13" s="8">
         <v>-40.9</v>
       </c>
-      <c r="P12" s="9">
+      <c r="P13" s="9">
         <v>8.1799999999999998E-2</v>
       </c>
-      <c r="Q12" s="8">
+      <c r="Q13" s="10">
         <v>105.3</v>
       </c>
     </row>
-    <row r="13" spans="1:17" s="5" customFormat="1">
-      <c r="A13" s="6">
+    <row r="14" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A14" s="6">
         <v>44501</v>
       </c>
-      <c r="B13" s="7">
+      <c r="B14" s="7">
         <v>38.9</v>
       </c>
-      <c r="C13" s="7">
+      <c r="C14" s="7">
         <v>40.5</v>
       </c>
-      <c r="D13" s="7">
+      <c r="D14" s="7">
         <v>41.5</v>
       </c>
-      <c r="E13" s="7">
+      <c r="E14" s="7">
         <v>37.799999999999997</v>
       </c>
-      <c r="F13" s="8">
+      <c r="F14" s="10">
         <v>1.6</v>
       </c>
-      <c r="G13" s="8">
+      <c r="G14" s="10">
         <v>4.1100000000000003</v>
       </c>
-      <c r="H13" s="9">
+      <c r="H14" s="9">
         <v>5.4999999999999997E-3</v>
       </c>
-      <c r="I13" s="10">
+      <c r="I14" s="8">
         <v>-37.6</v>
       </c>
-      <c r="J13" s="10">
+      <c r="J14" s="8">
         <v>-30.6</v>
       </c>
-      <c r="K13" s="9">
+      <c r="K14" s="9">
         <v>7.9000000000000001E-2</v>
       </c>
-      <c r="L13" s="8">
+      <c r="L14" s="10">
         <v>125.2</v>
       </c>
-      <c r="M13" s="9">
+      <c r="M14" s="9">
         <v>5.4999999999999997E-3</v>
       </c>
-      <c r="N13" s="10">
+      <c r="N14" s="8">
         <v>-37.6</v>
       </c>
-      <c r="O13" s="10">
+      <c r="O14" s="8">
         <v>-30.6</v>
       </c>
-      <c r="P13" s="9">
+      <c r="P14" s="9">
         <v>7.9000000000000001E-2</v>
       </c>
-      <c r="Q13" s="8">
+      <c r="Q14" s="10">
         <v>125.2</v>
       </c>
     </row>
-    <row r="14" spans="1:17" s="5" customFormat="1">
-      <c r="A14" s="6">
+    <row r="15" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A15" s="6">
         <v>44470</v>
       </c>
-      <c r="B14" s="7">
+      <c r="B15" s="7">
         <v>35.5</v>
       </c>
-      <c r="C14" s="7">
+      <c r="C15" s="7">
         <v>38.9</v>
       </c>
-      <c r="D14" s="7">
+      <c r="D15" s="7">
         <v>38.9</v>
       </c>
-      <c r="E14" s="7">
+      <c r="E15" s="7">
         <v>34.299999999999997</v>
       </c>
-      <c r="F14" s="8">
+      <c r="F15" s="10">
         <v>3.4</v>
       </c>
-      <c r="G14" s="8">
+      <c r="G15" s="10">
         <v>9.58</v>
       </c>
-      <c r="H14" s="9">
+      <c r="H15" s="9">
         <v>8.8000000000000005E-3</v>
       </c>
-      <c r="I14" s="10">
+      <c r="I15" s="8">
         <v>-25.8</v>
       </c>
-      <c r="J14" s="8">
+      <c r="J15" s="10">
         <v>58.4</v>
       </c>
-      <c r="K14" s="9">
+      <c r="K15" s="9">
         <v>7.3400000000000007E-2</v>
       </c>
-      <c r="L14" s="8">
+      <c r="L15" s="10">
         <v>170.7</v>
       </c>
-      <c r="M14" s="9">
+      <c r="M15" s="9">
         <v>8.8000000000000005E-3</v>
       </c>
-      <c r="N14" s="10">
+      <c r="N15" s="8">
         <v>-25.8</v>
       </c>
-      <c r="O14" s="8">
+      <c r="O15" s="10">
         <v>58.4</v>
       </c>
-      <c r="P14" s="9">
+      <c r="P15" s="9">
         <v>7.3400000000000007E-2</v>
       </c>
-      <c r="Q14" s="8">
+      <c r="Q15" s="10">
         <v>170.7</v>
       </c>
     </row>
-    <row r="15" spans="1:17" s="5" customFormat="1">
-      <c r="A15" s="6">
+    <row r="16" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A16" s="6">
         <v>44440</v>
       </c>
-      <c r="B15" s="7">
+      <c r="B16" s="7">
         <v>36.9</v>
       </c>
-      <c r="C15" s="7">
+      <c r="C16" s="7">
         <v>35.5</v>
       </c>
-      <c r="D15" s="7">
+      <c r="D16" s="7">
         <v>36.700000000000003</v>
       </c>
-      <c r="E15" s="7">
+      <c r="E16" s="7">
         <v>33.9</v>
       </c>
-      <c r="F15" s="10">
+      <c r="F16" s="8">
         <v>-1.4</v>
       </c>
-      <c r="G15" s="10">
+      <c r="G16" s="8">
         <v>-3.79</v>
       </c>
-      <c r="H15" s="9">
+      <c r="H16" s="9">
         <v>1.1900000000000001E-2</v>
       </c>
-      <c r="I15" s="8">
+      <c r="I16" s="10">
         <v>162.19999999999999</v>
       </c>
-      <c r="J15" s="8">
+      <c r="J16" s="10">
         <v>11780</v>
       </c>
-      <c r="K15" s="9">
+      <c r="K16" s="9">
         <v>6.4600000000000005E-2</v>
       </c>
-      <c r="L15" s="8">
+      <c r="L16" s="10">
         <v>199.7</v>
       </c>
-      <c r="M15" s="9">
+      <c r="M16" s="9">
         <v>1.1900000000000001E-2</v>
       </c>
-      <c r="N15" s="8">
+      <c r="N16" s="10">
         <v>162.19999999999999</v>
       </c>
-      <c r="O15" s="8">
+      <c r="O16" s="10">
         <v>11780</v>
       </c>
-      <c r="P15" s="9">
+      <c r="P16" s="9">
         <v>6.4600000000000005E-2</v>
       </c>
-      <c r="Q15" s="8">
+      <c r="Q16" s="10">
         <v>199.7</v>
       </c>
     </row>
-    <row r="16" spans="1:17" s="5" customFormat="1">
-      <c r="A16" s="6">
+    <row r="17" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A17" s="6">
         <v>44409</v>
       </c>
-      <c r="B16" s="7">
+      <c r="B17" s="7">
         <v>37.6</v>
       </c>
-      <c r="C16" s="7">
+      <c r="C17" s="7">
         <v>36.9</v>
       </c>
-      <c r="D16" s="7">
+      <c r="D17" s="7">
         <v>37.700000000000003</v>
       </c>
-      <c r="E16" s="7">
+      <c r="E17" s="7">
         <v>35.25</v>
       </c>
-      <c r="F16" s="10">
+      <c r="F17" s="8">
         <v>-0.7</v>
       </c>
-      <c r="G16" s="10">
+      <c r="G17" s="8">
         <v>-1.86</v>
       </c>
-      <c r="H16" s="9">
+      <c r="H17" s="9">
         <v>4.4999999999999997E-3</v>
       </c>
-      <c r="I16" s="10">
+      <c r="I17" s="8">
         <v>-51.8</v>
       </c>
-      <c r="J16" s="8">
+      <c r="J17" s="10">
         <v>0.89</v>
       </c>
-      <c r="K16" s="9">
+      <c r="K17" s="9">
         <v>5.28E-2</v>
       </c>
-      <c r="L16" s="8">
+      <c r="L17" s="10">
         <v>145.69999999999999</v>
       </c>
-      <c r="M16" s="9">
+      <c r="M17" s="9">
         <v>4.4999999999999997E-3</v>
       </c>
-      <c r="N16" s="10">
+      <c r="N17" s="8">
         <v>-51.8</v>
       </c>
-      <c r="O16" s="8">
+      <c r="O17" s="10">
         <v>0.89</v>
       </c>
-      <c r="P16" s="9">
+      <c r="P17" s="9">
         <v>5.28E-2</v>
       </c>
-      <c r="Q16" s="8">
+      <c r="Q17" s="10">
         <v>145.69999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:17" s="5" customFormat="1">
-      <c r="A17" s="6">
+    <row r="18" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A18" s="6">
         <v>44378</v>
       </c>
-      <c r="B17" s="7">
+      <c r="B18" s="7">
         <v>37</v>
       </c>
-      <c r="C17" s="7">
+      <c r="C18" s="7">
         <v>37.6</v>
       </c>
-      <c r="D17" s="7">
+      <c r="D18" s="7">
         <v>38.1</v>
       </c>
-      <c r="E17" s="7">
+      <c r="E18" s="7">
         <v>34.299999999999997</v>
       </c>
-      <c r="F17" s="8">
+      <c r="F18" s="10">
         <v>0.6</v>
       </c>
-      <c r="G17" s="8">
+      <c r="G18" s="10">
         <v>1.62</v>
       </c>
-      <c r="H17" s="9">
+      <c r="H18" s="9">
         <v>9.4000000000000004E-3</v>
       </c>
-      <c r="I17" s="8">
+      <c r="I18" s="10">
         <v>102.8</v>
       </c>
-      <c r="J17" s="8">
+      <c r="J18" s="10">
         <v>372.9</v>
       </c>
-      <c r="K17" s="9">
+      <c r="K18" s="9">
         <v>4.82E-2</v>
       </c>
-      <c r="L17" s="8">
+      <c r="L18" s="10">
         <v>184</v>
       </c>
-      <c r="M17" s="9">
+      <c r="M18" s="9">
         <v>9.4000000000000004E-3</v>
       </c>
-      <c r="N17" s="8">
+      <c r="N18" s="10">
         <v>102.8</v>
       </c>
-      <c r="O17" s="8">
+      <c r="O18" s="10">
         <v>372.9</v>
       </c>
-      <c r="P17" s="9">
+      <c r="P18" s="9">
         <v>4.82E-2</v>
       </c>
-      <c r="Q17" s="8">
+      <c r="Q18" s="10">
         <v>184</v>
       </c>
     </row>
-    <row r="18" spans="1:17" s="5" customFormat="1">
-      <c r="A18" s="6">
+    <row r="19" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A19" s="6">
         <v>44348</v>
       </c>
-      <c r="B18" s="7">
+      <c r="B19" s="7">
         <v>39</v>
       </c>
-      <c r="C18" s="7">
+      <c r="C19" s="7">
         <v>37</v>
       </c>
-      <c r="D18" s="7">
+      <c r="D19" s="7">
         <v>41.1</v>
       </c>
-      <c r="E18" s="7">
+      <c r="E19" s="7">
         <v>35.799999999999997</v>
       </c>
-      <c r="F18" s="10">
+      <c r="F19" s="8">
         <v>-2</v>
       </c>
-      <c r="G18" s="10">
+      <c r="G19" s="8">
         <v>-5.13</v>
       </c>
-      <c r="H18" s="9">
+      <c r="H19" s="9">
         <v>4.5999999999999999E-3</v>
       </c>
-      <c r="I18" s="10">
+      <c r="I19" s="8">
         <v>-30.2</v>
       </c>
-      <c r="J18" s="8">
+      <c r="J19" s="10">
         <v>238.7</v>
       </c>
-      <c r="K18" s="9">
+      <c r="K19" s="9">
         <v>3.8800000000000001E-2</v>
       </c>
-      <c r="L18" s="8">
+      <c r="L19" s="10">
         <v>159</v>
       </c>
-      <c r="M18" s="9">
+      <c r="M19" s="9">
         <v>4.5999999999999999E-3</v>
       </c>
-      <c r="N18" s="10">
+      <c r="N19" s="8">
         <v>-30.2</v>
       </c>
-      <c r="O18" s="8">
+      <c r="O19" s="10">
         <v>238.7</v>
       </c>
-      <c r="P18" s="9">
+      <c r="P19" s="9">
         <v>3.8800000000000001E-2</v>
       </c>
-      <c r="Q18" s="8">
+      <c r="Q19" s="10">
         <v>159</v>
       </c>
     </row>
-    <row r="19" spans="1:17" s="5" customFormat="1">
-      <c r="A19" s="6">
+    <row r="20" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A20" s="6">
         <v>44317</v>
       </c>
-      <c r="B19" s="7">
+      <c r="B20" s="7">
         <v>38.35</v>
       </c>
-      <c r="C19" s="7">
+      <c r="C20" s="7">
         <v>39</v>
       </c>
-      <c r="D19" s="7">
+      <c r="D20" s="7">
         <v>44.6</v>
       </c>
-      <c r="E19" s="7">
+      <c r="E20" s="7">
         <v>34.799999999999997</v>
       </c>
-      <c r="F19" s="8">
+      <c r="F20" s="10">
         <v>0.65</v>
       </c>
-      <c r="G19" s="8">
+      <c r="G20" s="10">
         <v>1.69</v>
       </c>
-      <c r="H19" s="9">
+      <c r="H20" s="9">
         <v>6.6E-3</v>
       </c>
-      <c r="I19" s="10">
+      <c r="I20" s="8">
         <v>-14.7</v>
       </c>
-      <c r="J19" s="8">
+      <c r="J20" s="10">
         <v>655.7</v>
       </c>
-      <c r="K19" s="9">
+      <c r="K20" s="9">
         <v>3.4200000000000001E-2</v>
       </c>
-      <c r="L19" s="8">
+      <c r="L20" s="10">
         <v>151</v>
       </c>
-      <c r="M19" s="9">
+      <c r="M20" s="9">
         <v>6.6E-3</v>
       </c>
-      <c r="N19" s="10">
+      <c r="N20" s="8">
         <v>-14.7</v>
       </c>
-      <c r="O19" s="8">
+      <c r="O20" s="10">
         <v>655.7</v>
       </c>
-      <c r="P19" s="9">
+      <c r="P20" s="9">
         <v>3.4200000000000001E-2</v>
       </c>
-      <c r="Q19" s="8">
+      <c r="Q20" s="10">
         <v>151</v>
       </c>
     </row>
-    <row r="20" spans="1:17" s="5" customFormat="1">
-      <c r="A20" s="6">
+    <row r="21" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A21" s="6">
         <v>44287</v>
       </c>
-      <c r="B20" s="7">
+      <c r="B21" s="7">
         <v>30</v>
       </c>
-      <c r="C20" s="7">
+      <c r="C21" s="7">
         <v>38.35</v>
       </c>
-      <c r="D20" s="7">
+      <c r="D21" s="7">
         <v>47.3</v>
       </c>
-      <c r="E20" s="7">
+      <c r="E21" s="7">
         <v>29.1</v>
       </c>
-      <c r="F20" s="8">
+      <c r="F21" s="10">
         <v>8.35</v>
       </c>
-      <c r="G20" s="8">
+      <c r="G21" s="10">
         <v>27.83</v>
       </c>
-      <c r="H20" s="9">
+      <c r="H21" s="9">
         <v>7.7999999999999996E-3</v>
       </c>
-      <c r="I20" s="8">
+      <c r="I21" s="10">
         <v>17.100000000000001</v>
       </c>
-      <c r="J20" s="8">
+      <c r="J21" s="10">
         <v>338.2</v>
       </c>
-      <c r="K20" s="9">
+      <c r="K21" s="9">
         <v>2.75E-2</v>
       </c>
-      <c r="L20" s="8">
+      <c r="L21" s="10">
         <v>116.1</v>
       </c>
-      <c r="M20" s="9">
+      <c r="M21" s="9">
         <v>7.7999999999999996E-3</v>
       </c>
-      <c r="N20" s="8">
+      <c r="N21" s="10">
         <v>17.100000000000001</v>
       </c>
-      <c r="O20" s="8">
+      <c r="O21" s="10">
         <v>338.2</v>
       </c>
-      <c r="P20" s="9">
+      <c r="P21" s="9">
         <v>2.75E-2</v>
       </c>
-      <c r="Q20" s="8">
+      <c r="Q21" s="10">
         <v>116.1</v>
       </c>
     </row>
-    <row r="21" spans="1:17" s="5" customFormat="1">
-      <c r="A21" s="6">
+    <row r="22" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A22" s="6">
         <v>44256</v>
       </c>
-      <c r="B21" s="7">
+      <c r="B22" s="7">
         <v>38.5</v>
       </c>
-      <c r="C21" s="7">
+      <c r="C22" s="7">
         <v>30</v>
       </c>
-      <c r="D21" s="7">
+      <c r="D22" s="7">
         <v>38.9</v>
       </c>
-      <c r="E21" s="7">
+      <c r="E22" s="7">
         <v>29</v>
       </c>
-      <c r="F21" s="10">
+      <c r="F22" s="8">
         <v>-8.5</v>
       </c>
-      <c r="G21" s="10">
+      <c r="G22" s="8">
         <v>-22.08</v>
       </c>
-      <c r="H21" s="9">
+      <c r="H22" s="9">
         <v>6.7000000000000002E-3</v>
       </c>
-      <c r="I21" s="8">
+      <c r="I22" s="10">
         <v>119.8</v>
       </c>
-      <c r="J21" s="8">
+      <c r="J22" s="10">
         <v>93</v>
       </c>
-      <c r="K21" s="9">
+      <c r="K22" s="9">
         <v>1.9699999999999999E-2</v>
       </c>
-      <c r="L21" s="8">
+      <c r="L22" s="10">
         <v>80</v>
       </c>
-      <c r="M21" s="9">
+      <c r="M22" s="9">
         <v>6.7000000000000002E-3</v>
       </c>
-      <c r="N21" s="8">
+      <c r="N22" s="10">
         <v>119.8</v>
       </c>
-      <c r="O21" s="8">
+      <c r="O22" s="10">
         <v>93</v>
       </c>
-      <c r="P21" s="9">
+      <c r="P22" s="9">
         <v>1.9699999999999999E-2</v>
       </c>
-      <c r="Q21" s="8">
+      <c r="Q22" s="10">
         <v>80</v>
       </c>
     </row>
-    <row r="22" spans="1:17" s="5" customFormat="1">
-      <c r="A22" s="6">
+    <row r="23" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A23" s="6">
         <v>44228</v>
       </c>
-      <c r="B22" s="7">
+      <c r="B23" s="7">
         <v>39.5</v>
       </c>
-      <c r="C22" s="7">
+      <c r="C23" s="7">
         <v>38.5</v>
       </c>
-      <c r="D22" s="7">
+      <c r="D23" s="7">
         <v>40.15</v>
       </c>
-      <c r="E22" s="7">
+      <c r="E23" s="7">
         <v>38</v>
       </c>
-      <c r="F22" s="10">
+      <c r="F23" s="8">
         <v>-1</v>
       </c>
-      <c r="G22" s="10">
+      <c r="G23" s="8">
         <v>-2.5299999999999998</v>
       </c>
-      <c r="H22" s="9">
+      <c r="H23" s="9">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="I22" s="10">
+      <c r="I23" s="8">
         <v>-69.8</v>
       </c>
-      <c r="J22" s="10">
+      <c r="J23" s="8">
         <v>-1.62</v>
       </c>
-      <c r="K22" s="9">
+      <c r="K23" s="9">
         <v>1.3100000000000001E-2</v>
       </c>
-      <c r="L22" s="8">
+      <c r="L23" s="10">
         <v>74</v>
       </c>
-      <c r="M22" s="9">
+      <c r="M23" s="9">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="N22" s="10">
+      <c r="N23" s="8">
         <v>-69.8</v>
       </c>
-      <c r="O22" s="10">
+      <c r="O23" s="8">
         <v>-1.62</v>
       </c>
-      <c r="P22" s="9">
+      <c r="P23" s="9">
         <v>1.3100000000000001E-2</v>
       </c>
-      <c r="Q22" s="8">
+      <c r="Q23" s="10">
         <v>74</v>
       </c>
     </row>
-    <row r="23" spans="1:17" s="5" customFormat="1">
-      <c r="A23" s="6">
+    <row r="24" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A24" s="6">
         <v>44197</v>
       </c>
-      <c r="B23" s="7">
+      <c r="B24" s="7">
         <v>43</v>
       </c>
-      <c r="C23" s="7">
+      <c r="C24" s="7">
         <v>39.5</v>
       </c>
-      <c r="D23" s="7">
+      <c r="D24" s="7">
         <v>42</v>
       </c>
-      <c r="E23" s="7">
+      <c r="E24" s="7">
         <v>37.35</v>
       </c>
-      <c r="F23" s="10">
+      <c r="F24" s="8">
         <v>-3.5</v>
       </c>
-      <c r="G23" s="10">
+      <c r="G24" s="8">
         <v>-8.14</v>
       </c>
-      <c r="H23" s="9">
+      <c r="H24" s="9">
         <v>0.01</v>
       </c>
-      <c r="I23" s="8">
+      <c r="I24" s="10">
         <v>110.5</v>
       </c>
-      <c r="J23" s="8">
+      <c r="J24" s="10">
         <v>126.6</v>
       </c>
-      <c r="K23" s="9">
+      <c r="K24" s="9">
         <v>0.01</v>
       </c>
-      <c r="L23" s="8">
+      <c r="L24" s="10">
         <v>126.6</v>
       </c>
-      <c r="M23" s="9">
+      <c r="M24" s="9">
         <v>0.01</v>
       </c>
-      <c r="N23" s="8">
+      <c r="N24" s="10">
         <v>110.5</v>
       </c>
-      <c r="O23" s="8">
+      <c r="O24" s="10">
         <v>126.6</v>
       </c>
-      <c r="P23" s="9">
+      <c r="P24" s="9">
         <v>0.01</v>
       </c>
-      <c r="Q23" s="8">
+      <c r="Q24" s="10">
         <v>126.6</v>
       </c>
     </row>
-    <row r="24" spans="1:17" s="5" customFormat="1">
-      <c r="A24" s="6">
+    <row r="25" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A25" s="6">
         <v>44166</v>
       </c>
-      <c r="B24" s="7">
+      <c r="B25" s="7">
         <v>46</v>
       </c>
-      <c r="C24" s="7">
+      <c r="C25" s="7">
         <v>43</v>
       </c>
-      <c r="D24" s="7">
+      <c r="D25" s="7">
         <v>46.7</v>
       </c>
-      <c r="E24" s="7">
+      <c r="E25" s="7">
         <v>39.700000000000003</v>
       </c>
-      <c r="F24" s="10">
+      <c r="F25" s="8">
         <v>-3</v>
       </c>
-      <c r="G24" s="10">
+      <c r="G25" s="8">
         <v>-6.52</v>
       </c>
-      <c r="H24" s="9">
+      <c r="H25" s="9">
         <v>4.7999999999999996E-3</v>
       </c>
-      <c r="I24" s="10">
+      <c r="I25" s="8">
         <v>-39.799999999999997</v>
       </c>
-      <c r="J24" s="8">
+      <c r="J25" s="10">
         <v>44.1</v>
       </c>
-      <c r="K24" s="9">
+      <c r="K25" s="9">
         <v>3.9800000000000002E-2</v>
       </c>
-      <c r="L24" s="10">
+      <c r="L25" s="8">
         <v>-74.7</v>
       </c>
-      <c r="M24" s="9">
+      <c r="M25" s="9">
         <v>4.7999999999999996E-3</v>
       </c>
-      <c r="N24" s="10">
+      <c r="N25" s="8">
         <v>-39.799999999999997</v>
       </c>
-      <c r="O24" s="8">
+      <c r="O25" s="10">
         <v>44.1</v>
       </c>
-      <c r="P24" s="9">
+      <c r="P25" s="9">
         <v>3.9800000000000002E-2</v>
       </c>
-      <c r="Q24" s="10">
+      <c r="Q25" s="8">
         <v>-74.7</v>
       </c>
     </row>
-    <row r="25" spans="1:17" s="5" customFormat="1">
-      <c r="A25" s="6">
+    <row r="26" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A26" s="6">
         <v>44136</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E25" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F25" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G25" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="H25" s="9">
-        <v>7.9000000000000008E-3</v>
-      </c>
-      <c r="I25" s="8">
-        <v>42.4</v>
-      </c>
-      <c r="J25" s="10">
-        <v>-57.1</v>
-      </c>
-      <c r="K25" s="9">
-        <v>3.5000000000000003E-2</v>
-      </c>
-      <c r="L25" s="10">
-        <v>-77.2</v>
-      </c>
-      <c r="M25" s="9">
-        <v>7.9000000000000008E-3</v>
-      </c>
-      <c r="N25" s="8">
-        <v>42.4</v>
-      </c>
-      <c r="O25" s="10">
-        <v>-57.1</v>
-      </c>
-      <c r="P25" s="9">
-        <v>3.5000000000000003E-2</v>
-      </c>
-      <c r="Q25" s="10">
-        <v>-77.2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:17" s="5" customFormat="1">
-      <c r="A26" s="6">
-        <v>44105</v>
       </c>
       <c r="B26" s="7" t="s">
         <v>17</v>
@@ -2519,39 +2527,39 @@
         <v>17</v>
       </c>
       <c r="H26" s="9">
-        <v>5.5999999999999999E-3</v>
-      </c>
-      <c r="I26" s="8">
-        <v>5460</v>
-      </c>
-      <c r="J26" s="10">
-        <v>-30</v>
+        <v>7.9000000000000008E-3</v>
+      </c>
+      <c r="I26" s="10">
+        <v>42.4</v>
+      </c>
+      <c r="J26" s="8">
+        <v>-57.1</v>
       </c>
       <c r="K26" s="9">
-        <v>2.7099999999999999E-2</v>
-      </c>
-      <c r="L26" s="10">
-        <v>-80</v>
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="L26" s="8">
+        <v>-77.2</v>
       </c>
       <c r="M26" s="9">
-        <v>5.5999999999999999E-3</v>
-      </c>
-      <c r="N26" s="8">
-        <v>5460</v>
-      </c>
-      <c r="O26" s="10">
-        <v>-30</v>
+        <v>7.9000000000000008E-3</v>
+      </c>
+      <c r="N26" s="10">
+        <v>42.4</v>
+      </c>
+      <c r="O26" s="8">
+        <v>-57.1</v>
       </c>
       <c r="P26" s="9">
-        <v>2.7099999999999999E-2</v>
-      </c>
-      <c r="Q26" s="10">
-        <v>-80</v>
-      </c>
-    </row>
-    <row r="27" spans="1:17" s="5" customFormat="1">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="Q26" s="8">
+        <v>-77.2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
-        <v>44075</v>
+        <v>44105</v>
       </c>
       <c r="B27" s="7" t="s">
         <v>17</v>
@@ -2572,39 +2580,39 @@
         <v>17</v>
       </c>
       <c r="H27" s="9">
-        <v>1E-4</v>
+        <v>5.5999999999999999E-3</v>
       </c>
       <c r="I27" s="10">
-        <v>-97.8</v>
-      </c>
-      <c r="J27" s="10">
-        <v>-99.7</v>
+        <v>5460</v>
+      </c>
+      <c r="J27" s="8">
+        <v>-30</v>
       </c>
       <c r="K27" s="9">
-        <v>2.1600000000000001E-2</v>
-      </c>
-      <c r="L27" s="10">
-        <v>-83.1</v>
+        <v>2.7099999999999999E-2</v>
+      </c>
+      <c r="L27" s="8">
+        <v>-80</v>
       </c>
       <c r="M27" s="9">
-        <v>1E-4</v>
+        <v>5.5999999999999999E-3</v>
       </c>
       <c r="N27" s="10">
-        <v>-97.8</v>
-      </c>
-      <c r="O27" s="10">
-        <v>-99.7</v>
+        <v>5460</v>
+      </c>
+      <c r="O27" s="8">
+        <v>-30</v>
       </c>
       <c r="P27" s="9">
-        <v>2.1600000000000001E-2</v>
-      </c>
-      <c r="Q27" s="10">
-        <v>-83.1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17" s="5" customFormat="1">
+        <v>2.7099999999999999E-2</v>
+      </c>
+      <c r="Q27" s="8">
+        <v>-80</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
-        <v>44044</v>
+        <v>44075</v>
       </c>
       <c r="B28" s="7" t="s">
         <v>17</v>
@@ -2625,33 +2633,86 @@
         <v>17</v>
       </c>
       <c r="H28" s="9">
+        <v>1E-4</v>
+      </c>
+      <c r="I28" s="8">
+        <v>-97.8</v>
+      </c>
+      <c r="J28" s="8">
+        <v>-99.7</v>
+      </c>
+      <c r="K28" s="9">
+        <v>2.1600000000000001E-2</v>
+      </c>
+      <c r="L28" s="8">
+        <v>-83.1</v>
+      </c>
+      <c r="M28" s="9">
+        <v>1E-4</v>
+      </c>
+      <c r="N28" s="8">
+        <v>-97.8</v>
+      </c>
+      <c r="O28" s="8">
+        <v>-99.7</v>
+      </c>
+      <c r="P28" s="9">
+        <v>2.1600000000000001E-2</v>
+      </c>
+      <c r="Q28" s="8">
+        <v>-83.1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A29" s="6">
+        <v>44044</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F29" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G29" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H29" s="9">
         <v>4.4999999999999997E-3</v>
       </c>
-      <c r="I28" s="9" t="s">
+      <c r="I29" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="J28" s="10">
+      <c r="J29" s="8">
         <v>-83</v>
       </c>
-      <c r="K28" s="9">
+      <c r="K29" s="9">
         <v>2.1499999999999998E-2</v>
       </c>
-      <c r="L28" s="10">
+      <c r="L29" s="8">
         <v>-77</v>
       </c>
-      <c r="M28" s="9">
+      <c r="M29" s="9">
         <v>4.4999999999999997E-3</v>
       </c>
-      <c r="N28" s="9" t="s">
+      <c r="N29" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="O28" s="10">
+      <c r="O29" s="8">
         <v>-83</v>
       </c>
-      <c r="P28" s="9">
+      <c r="P29" s="9">
         <v>2.1499999999999998E-2</v>
       </c>
-      <c r="Q28" s="10">
+      <c r="Q29" s="8">
         <v>-77</v>
       </c>
     </row>
@@ -2670,7 +2731,7 @@
     <mergeCell ref="H2:J2"/>
     <mergeCell ref="K2:L2"/>
   </mergeCells>
-  <phoneticPr fontId="24" type="noConversion"/>
+  <phoneticPr fontId="25" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>